--- a/data/nzd0158/nzd0158.xlsx
+++ b/data/nzd0158/nzd0158.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L378"/>
+  <dimension ref="A1:L381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16308,6 +16308,132 @@
         <v>381.25</v>
       </c>
       <c r="L378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>385.68</v>
+      </c>
+      <c r="C379" t="n">
+        <v>379.27</v>
+      </c>
+      <c r="D379" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="E379" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="F379" t="n">
+        <v>375.37</v>
+      </c>
+      <c r="G379" t="n">
+        <v>370.37</v>
+      </c>
+      <c r="H379" t="n">
+        <v>367.82</v>
+      </c>
+      <c r="I379" t="n">
+        <v>367.83</v>
+      </c>
+      <c r="J379" t="n">
+        <v>364.07</v>
+      </c>
+      <c r="K379" t="n">
+        <v>381.86</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>386.18</v>
+      </c>
+      <c r="C380" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="D380" t="n">
+        <v>382.47</v>
+      </c>
+      <c r="E380" t="n">
+        <v>381.11</v>
+      </c>
+      <c r="F380" t="n">
+        <v>376.72</v>
+      </c>
+      <c r="G380" t="n">
+        <v>370.91</v>
+      </c>
+      <c r="H380" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="I380" t="n">
+        <v>368.59</v>
+      </c>
+      <c r="J380" t="n">
+        <v>364.29</v>
+      </c>
+      <c r="K380" t="n">
+        <v>381.2</v>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>385.38</v>
+      </c>
+      <c r="C381" t="n">
+        <v>379.04</v>
+      </c>
+      <c r="D381" t="n">
+        <v>381.21</v>
+      </c>
+      <c r="E381" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="F381" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="G381" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="H381" t="n">
+        <v>368.65</v>
+      </c>
+      <c r="I381" t="n">
+        <v>368.16</v>
+      </c>
+      <c r="J381" t="n">
+        <v>364.13</v>
+      </c>
+      <c r="K381" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="L381" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16324,7 +16450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B392"/>
+  <dimension ref="A1:B395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20247,6 +20373,36 @@
       </c>
       <c r="B392" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -20415,28 +20571,28 @@
         <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1323125401419989</v>
+        <v>0.136877420165171</v>
       </c>
       <c r="J2" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K2" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04763028459752039</v>
+        <v>0.05154288957986319</v>
       </c>
       <c r="M2" t="n">
-        <v>3.435178838696747</v>
+        <v>3.430396155099926</v>
       </c>
       <c r="N2" t="n">
-        <v>18.83750882209141</v>
+        <v>18.7499317858364</v>
       </c>
       <c r="O2" t="n">
-        <v>4.340219904807982</v>
+        <v>4.330119142221886</v>
       </c>
       <c r="P2" t="n">
-        <v>379.3664910660457</v>
+        <v>379.3164576055603</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20493,28 +20649,28 @@
         <v>0.1104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0562679956049555</v>
+        <v>0.05623401434512818</v>
       </c>
       <c r="J3" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K3" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01338649976031836</v>
+        <v>0.01361652577507999</v>
       </c>
       <c r="M3" t="n">
-        <v>2.744697810095876</v>
+        <v>2.724547953032477</v>
       </c>
       <c r="N3" t="n">
-        <v>12.55746461889548</v>
+        <v>12.45847212961859</v>
       </c>
       <c r="O3" t="n">
-        <v>3.543651311697509</v>
+        <v>3.529656092258648</v>
       </c>
       <c r="P3" t="n">
-        <v>377.8022557777103</v>
+        <v>377.8026294607134</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20571,28 +20727,28 @@
         <v>0.1999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04016173518454366</v>
+        <v>-0.03198618023461357</v>
       </c>
       <c r="J4" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K4" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00804037501007937</v>
+        <v>0.005115471830230756</v>
       </c>
       <c r="M4" t="n">
-        <v>2.574611360532436</v>
+        <v>2.591721316993396</v>
       </c>
       <c r="N4" t="n">
-        <v>10.70882154150361</v>
+        <v>10.82178434145928</v>
       </c>
       <c r="O4" t="n">
-        <v>3.272433580915526</v>
+        <v>3.289648057385361</v>
       </c>
       <c r="P4" t="n">
-        <v>378.1532660946638</v>
+        <v>378.0636620546435</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20649,28 +20805,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04540488610469795</v>
+        <v>0.05023961243028535</v>
       </c>
       <c r="J5" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K5" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007975636568990696</v>
+        <v>0.009876083462447727</v>
       </c>
       <c r="M5" t="n">
-        <v>2.884683395610538</v>
+        <v>2.881180783661705</v>
       </c>
       <c r="N5" t="n">
-        <v>13.79943222259317</v>
+        <v>13.76209323171526</v>
       </c>
       <c r="O5" t="n">
-        <v>3.714758703145221</v>
+        <v>3.709729536194688</v>
       </c>
       <c r="P5" t="n">
-        <v>375.9461461210388</v>
+        <v>375.8931516250852</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20727,28 +20883,28 @@
         <v>0.1058</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07121246858808296</v>
+        <v>0.07464066506734758</v>
       </c>
       <c r="J6" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K6" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02911892223362145</v>
+        <v>0.03234801177407232</v>
       </c>
       <c r="M6" t="n">
-        <v>2.376488751548587</v>
+        <v>2.371907046818991</v>
       </c>
       <c r="N6" t="n">
-        <v>9.099172038037805</v>
+        <v>9.063787957806685</v>
       </c>
       <c r="O6" t="n">
-        <v>3.01648338931906</v>
+        <v>3.010612555246305</v>
       </c>
       <c r="P6" t="n">
-        <v>371.9646280395623</v>
+        <v>371.9270492651646</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20805,28 +20961,28 @@
         <v>0.0876</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1272466223066714</v>
+        <v>0.1298649507260264</v>
       </c>
       <c r="J7" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K7" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04946575589131241</v>
+        <v>0.05226577446475877</v>
       </c>
       <c r="M7" t="n">
-        <v>3.194785497203114</v>
+        <v>3.177409517184429</v>
       </c>
       <c r="N7" t="n">
-        <v>16.74382583004645</v>
+        <v>16.6318369951845</v>
       </c>
       <c r="O7" t="n">
-        <v>4.091922021501198</v>
+        <v>4.078214927536863</v>
       </c>
       <c r="P7" t="n">
-        <v>365.4767507856087</v>
+        <v>365.4480520417715</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20883,28 +21039,28 @@
         <v>0.0589</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1163685810598138</v>
+        <v>-0.1123512646079734</v>
       </c>
       <c r="J8" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K8" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02906608583087689</v>
+        <v>0.02758438900761251</v>
       </c>
       <c r="M8" t="n">
-        <v>3.875359797143998</v>
+        <v>3.865641369656432</v>
       </c>
       <c r="N8" t="n">
-        <v>24.57471829347251</v>
+        <v>24.42970089728823</v>
       </c>
       <c r="O8" t="n">
-        <v>4.957289409896553</v>
+        <v>4.94264108521833</v>
       </c>
       <c r="P8" t="n">
-        <v>369.06235887427</v>
+        <v>369.0186001632936</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20961,28 +21117,28 @@
         <v>0.0837</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05332707470669139</v>
+        <v>-0.05242523085943451</v>
       </c>
       <c r="J9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009815410231346022</v>
+        <v>0.009662160105012751</v>
       </c>
       <c r="M9" t="n">
-        <v>2.821163930983635</v>
+        <v>2.803972076535211</v>
       </c>
       <c r="N9" t="n">
-        <v>15.58537227818014</v>
+        <v>15.46548389048851</v>
       </c>
       <c r="O9" t="n">
-        <v>3.947831338618729</v>
+        <v>3.932617943620828</v>
       </c>
       <c r="P9" t="n">
-        <v>369.0731923012721</v>
+        <v>369.0633682168065</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21039,28 +21195,28 @@
         <v>0.076</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04970457001040161</v>
+        <v>-0.05159009986759028</v>
       </c>
       <c r="J10" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K10" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006025778486510869</v>
+        <v>0.006605308870496041</v>
       </c>
       <c r="M10" t="n">
-        <v>3.60007944950828</v>
+        <v>3.578855833323227</v>
       </c>
       <c r="N10" t="n">
-        <v>22.1395379058099</v>
+        <v>21.97531491574937</v>
       </c>
       <c r="O10" t="n">
-        <v>4.705267038735411</v>
+        <v>4.687783582435239</v>
       </c>
       <c r="P10" t="n">
-        <v>366.6752763707026</v>
+        <v>366.6958122624519</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21117,28 +21273,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.135655948600065</v>
+        <v>-0.1292602712245852</v>
       </c>
       <c r="J11" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K11" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06292631690650985</v>
+        <v>0.05802957886250493</v>
       </c>
       <c r="M11" t="n">
-        <v>3.142956226930814</v>
+        <v>3.146697261081759</v>
       </c>
       <c r="N11" t="n">
-        <v>14.74749194304995</v>
+        <v>14.75044450244288</v>
       </c>
       <c r="O11" t="n">
-        <v>3.840246338849886</v>
+        <v>3.840630742787293</v>
       </c>
       <c r="P11" t="n">
-        <v>381.2200797259059</v>
+        <v>381.1499798410885</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21176,7 +21332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L378"/>
+  <dimension ref="A1:L381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44587,6 +44743,192 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-36.72664970073493,175.70209493811174</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-36.72664226429564,175.70299738223207</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-36.72654784662956,175.70388614890177</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-36.726500885419995,175.70477869700116</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-36.72644244780762,175.7056729550607</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-36.726391346998426,175.70657034157165</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>-36.726301324096404,175.70746003529024</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>-36.72617063080544,175.70834011194992</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>-36.72604475230202,175.7092263713984</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>-36.72578053906997,175.710082064002</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-36.72664522313981,175.70209433095394</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-36.72663939863807,175.70299699362928</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-36.726549009830855,175.70388631746175</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-36.72648651933027,175.70477622297057</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-36.72643042696546,175.7056706656409</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-36.72638654811928,175.7065693522183</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>-36.72629309629549,175.707458074879</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>-36.726163951892815,175.70833824250235</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>-36.72604281134806,175.70922587390967</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>-36.72578640283189,175.710083284556</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-36.726652387292,175.7020953024065</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-36.726644323987024,175.70299766154037</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-36.72656028393558,175.70388795119732</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-36.72649803004814,175.7047782052683</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-36.726437728514036,175.70567205625133</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>-36.72639205794349,175.70657048814257</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>-36.726293981005284,175.7074582856759</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>-36.72616773075128,175.70833930021604</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>-36.72604422295094,175.70922623571963</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>-36.72578462593434,175.71008291469113</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0158/nzd0158.xlsx
+++ b/data/nzd0158/nzd0158.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L381"/>
+  <dimension ref="A1:L382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16436,6 +16436,48 @@
       <c r="L381" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="C382" t="n">
+        <v>379.96</v>
+      </c>
+      <c r="D382" t="n">
+        <v>381.51</v>
+      </c>
+      <c r="E382" t="n">
+        <v>381.24</v>
+      </c>
+      <c r="F382" t="n">
+        <v>376.85</v>
+      </c>
+      <c r="G382" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="H382" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="I382" t="n">
+        <v>369.08</v>
+      </c>
+      <c r="J382" t="n">
+        <v>365.86</v>
+      </c>
+      <c r="K382" t="n">
+        <v>382.12</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B395"/>
+  <dimension ref="A1:B396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20403,6 +20445,16 @@
       </c>
       <c r="B395" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -20571,28 +20623,28 @@
         <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.136877420165171</v>
+        <v>0.1386324995387388</v>
       </c>
       <c r="J2" t="n">
+        <v>381</v>
+      </c>
+      <c r="K2" t="n">
         <v>380</v>
       </c>
-      <c r="K2" t="n">
-        <v>379</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.05154288957986319</v>
+        <v>0.0530337105422215</v>
       </c>
       <c r="M2" t="n">
-        <v>3.430396155099926</v>
+        <v>3.429986151610969</v>
       </c>
       <c r="N2" t="n">
-        <v>18.7499317858364</v>
+        <v>18.7281619443688</v>
       </c>
       <c r="O2" t="n">
-        <v>4.330119142221886</v>
+        <v>4.327604642798231</v>
       </c>
       <c r="P2" t="n">
-        <v>379.3164576055603</v>
+        <v>379.297187089298</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20649,28 +20701,28 @@
         <v>0.1104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05623401434512818</v>
+        <v>0.05657569420072733</v>
       </c>
       <c r="J3" t="n">
+        <v>381</v>
+      </c>
+      <c r="K3" t="n">
         <v>380</v>
       </c>
-      <c r="K3" t="n">
-        <v>379</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01361652577507999</v>
+        <v>0.01386191205041243</v>
       </c>
       <c r="M3" t="n">
-        <v>2.724547953032477</v>
+        <v>2.719061213211023</v>
       </c>
       <c r="N3" t="n">
-        <v>12.45847212961859</v>
+        <v>12.42673167311419</v>
       </c>
       <c r="O3" t="n">
-        <v>3.529656092258648</v>
+        <v>3.525156971414774</v>
       </c>
       <c r="P3" t="n">
-        <v>377.8026294607134</v>
+        <v>377.7988778655929</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20727,28 +20779,28 @@
         <v>0.1999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03198618023461357</v>
+        <v>-0.02965855630542261</v>
       </c>
       <c r="J4" t="n">
+        <v>381</v>
+      </c>
+      <c r="K4" t="n">
         <v>380</v>
       </c>
-      <c r="K4" t="n">
-        <v>379</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.005115471830230756</v>
+        <v>0.004408211390557248</v>
       </c>
       <c r="M4" t="n">
-        <v>2.591721316993396</v>
+        <v>2.595708890515847</v>
       </c>
       <c r="N4" t="n">
-        <v>10.82178434145928</v>
+        <v>10.84180149044539</v>
       </c>
       <c r="O4" t="n">
-        <v>3.289648057385361</v>
+        <v>3.292689097143153</v>
       </c>
       <c r="P4" t="n">
-        <v>378.0636620546435</v>
+        <v>378.0381050824317</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20805,28 +20857,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05023961243028535</v>
+        <v>0.05239128823209022</v>
       </c>
       <c r="J5" t="n">
+        <v>381</v>
+      </c>
+      <c r="K5" t="n">
         <v>380</v>
       </c>
-      <c r="K5" t="n">
-        <v>379</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.009876083462447727</v>
+        <v>0.01076345014849411</v>
       </c>
       <c r="M5" t="n">
-        <v>2.881180783661705</v>
+        <v>2.882299833807132</v>
       </c>
       <c r="N5" t="n">
-        <v>13.76209323171526</v>
+        <v>13.76731815087232</v>
       </c>
       <c r="O5" t="n">
-        <v>3.709729536194688</v>
+        <v>3.710433687707182</v>
       </c>
       <c r="P5" t="n">
-        <v>375.8931516250852</v>
+        <v>375.869526537722</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20883,28 +20935,28 @@
         <v>0.1058</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07464066506734758</v>
+        <v>0.0762095656763679</v>
       </c>
       <c r="J6" t="n">
+        <v>381</v>
+      </c>
+      <c r="K6" t="n">
         <v>380</v>
       </c>
-      <c r="K6" t="n">
-        <v>379</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03234801177407232</v>
+        <v>0.03379468394020169</v>
       </c>
       <c r="M6" t="n">
-        <v>2.371907046818991</v>
+        <v>2.372132375511057</v>
       </c>
       <c r="N6" t="n">
-        <v>9.063787957806685</v>
+        <v>9.061968544410366</v>
       </c>
       <c r="O6" t="n">
-        <v>3.010612555246305</v>
+        <v>3.010310373434999</v>
       </c>
       <c r="P6" t="n">
-        <v>371.9270492651646</v>
+        <v>371.9098229646591</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20961,28 +21013,28 @@
         <v>0.0876</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1298649507260264</v>
+        <v>0.1311781178458767</v>
       </c>
       <c r="J7" t="n">
+        <v>381</v>
+      </c>
+      <c r="K7" t="n">
         <v>380</v>
       </c>
-      <c r="K7" t="n">
-        <v>379</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05226577446475877</v>
+        <v>0.0535317713576603</v>
       </c>
       <c r="M7" t="n">
-        <v>3.177409517184429</v>
+        <v>3.172982561514329</v>
       </c>
       <c r="N7" t="n">
-        <v>16.6318369951845</v>
+        <v>16.60350433856361</v>
       </c>
       <c r="O7" t="n">
-        <v>4.078214927536863</v>
+        <v>4.074739787834753</v>
       </c>
       <c r="P7" t="n">
-        <v>365.4480520417715</v>
+        <v>365.4336336577831</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21039,28 +21091,28 @@
         <v>0.0589</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1123512646079734</v>
+        <v>-0.1100214551392457</v>
       </c>
       <c r="J8" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K8" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02758438900761251</v>
+        <v>0.0265863071129826</v>
       </c>
       <c r="M8" t="n">
-        <v>3.865641369656432</v>
+        <v>3.867599851373734</v>
       </c>
       <c r="N8" t="n">
-        <v>24.42970089728823</v>
+        <v>24.41485357312586</v>
       </c>
       <c r="O8" t="n">
-        <v>4.94264108521833</v>
+        <v>4.941138894336595</v>
       </c>
       <c r="P8" t="n">
-        <v>369.0186001632936</v>
+        <v>368.9931808172197</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21117,28 +21169,28 @@
         <v>0.0837</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05242523085943451</v>
+        <v>-0.05165946841105869</v>
       </c>
       <c r="J9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009662160105012751</v>
+        <v>0.009437773948648309</v>
       </c>
       <c r="M9" t="n">
-        <v>2.803972076535211</v>
+        <v>2.800900929842944</v>
       </c>
       <c r="N9" t="n">
-        <v>15.46548389048851</v>
+        <v>15.43021502707849</v>
       </c>
       <c r="O9" t="n">
-        <v>3.932617943620828</v>
+        <v>3.928131238525323</v>
       </c>
       <c r="P9" t="n">
-        <v>369.0633682168065</v>
+        <v>369.0550133788049</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21195,28 +21247,28 @@
         <v>0.076</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05159009986759028</v>
+        <v>-0.05128984797499192</v>
       </c>
       <c r="J10" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K10" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006605308870496041</v>
+        <v>0.006568267464985622</v>
       </c>
       <c r="M10" t="n">
-        <v>3.578855833323227</v>
+        <v>3.57124309065383</v>
       </c>
       <c r="N10" t="n">
-        <v>21.97531491574937</v>
+        <v>21.91845526878436</v>
       </c>
       <c r="O10" t="n">
-        <v>4.687783582435239</v>
+        <v>4.68171499226345</v>
       </c>
       <c r="P10" t="n">
-        <v>366.6958122624519</v>
+        <v>366.69253636935</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21273,28 +21325,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1292602712245852</v>
+        <v>-0.1268502000155281</v>
       </c>
       <c r="J11" t="n">
+        <v>381</v>
+      </c>
+      <c r="K11" t="n">
         <v>380</v>
       </c>
-      <c r="K11" t="n">
-        <v>379</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.05802957886250493</v>
+        <v>0.05614087690000591</v>
       </c>
       <c r="M11" t="n">
-        <v>3.146697261081759</v>
+        <v>3.149574126357967</v>
       </c>
       <c r="N11" t="n">
-        <v>14.75044450244288</v>
+        <v>14.76361945921236</v>
       </c>
       <c r="O11" t="n">
-        <v>3.840630742787293</v>
+        <v>3.842345567386198</v>
       </c>
       <c r="P11" t="n">
-        <v>381.1499798410885</v>
+        <v>381.1235176097347</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21332,7 +21384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L381"/>
+  <dimension ref="A1:L382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44929,6 +44981,68 @@
         </is>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-36.726644417172686,175.70209422166556</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-36.72663608522151,175.70299654430735</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-36.726557599624925,175.7038875622126</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-36.72648535933545,175.70477602320418</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-36.72642926940287,175.70567044517827</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-36.72638228244892,175.70656847279324</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>-36.726279117880914,175.70745474428904</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>-36.72615964575175,175.70833703720078</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>-36.726028959994636,175.70922232365024</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>-36.725778229103156,175.71008158317775</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0158/nzd0158.xlsx
+++ b/data/nzd0158/nzd0158.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L382"/>
+  <dimension ref="A1:L383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16478,6 +16478,48 @@
       <c r="L382" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>386.54</v>
+      </c>
+      <c r="C383" t="n">
+        <v>380.98</v>
+      </c>
+      <c r="D383" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="E383" t="n">
+        <v>381.87</v>
+      </c>
+      <c r="F383" t="n">
+        <v>378.25</v>
+      </c>
+      <c r="G383" t="n">
+        <v>372.77</v>
+      </c>
+      <c r="H383" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="I383" t="n">
+        <v>367.49</v>
+      </c>
+      <c r="J383" t="n">
+        <v>365.75</v>
+      </c>
+      <c r="K383" t="n">
+        <v>381.66</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16492,7 +16534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B396"/>
+  <dimension ref="A1:B397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20455,6 +20497,16 @@
       </c>
       <c r="B396" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -20623,28 +20675,28 @@
         <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1386324995387388</v>
+        <v>0.1405110800561017</v>
       </c>
       <c r="J2" t="n">
+        <v>382</v>
+      </c>
+      <c r="K2" t="n">
         <v>381</v>
       </c>
-      <c r="K2" t="n">
-        <v>380</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0530337105422215</v>
+        <v>0.05463118533519085</v>
       </c>
       <c r="M2" t="n">
-        <v>3.429986151610969</v>
+        <v>3.430093220621183</v>
       </c>
       <c r="N2" t="n">
-        <v>18.7281619443688</v>
+        <v>18.71044980623944</v>
       </c>
       <c r="O2" t="n">
-        <v>4.327604642798231</v>
+        <v>4.325557745105184</v>
       </c>
       <c r="P2" t="n">
-        <v>379.297187089298</v>
+        <v>379.2764718397643</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20701,28 +20753,28 @@
         <v>0.1104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05657569420072733</v>
+        <v>0.05746303595113425</v>
       </c>
       <c r="J3" t="n">
+        <v>382</v>
+      </c>
+      <c r="K3" t="n">
         <v>381</v>
       </c>
-      <c r="K3" t="n">
-        <v>380</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01386191205041243</v>
+        <v>0.01437245998925474</v>
       </c>
       <c r="M3" t="n">
-        <v>2.719061213211023</v>
+        <v>2.716241932661028</v>
       </c>
       <c r="N3" t="n">
-        <v>12.42673167311419</v>
+        <v>12.40113091019356</v>
       </c>
       <c r="O3" t="n">
-        <v>3.525156971414774</v>
+        <v>3.521523947127658</v>
       </c>
       <c r="P3" t="n">
-        <v>377.7988778655929</v>
+        <v>377.7890930809583</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20779,28 +20831,28 @@
         <v>0.1999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02965855630542261</v>
+        <v>-0.02684860682812127</v>
       </c>
       <c r="J4" t="n">
+        <v>382</v>
+      </c>
+      <c r="K4" t="n">
         <v>381</v>
       </c>
-      <c r="K4" t="n">
-        <v>380</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.004408211390557248</v>
+        <v>0.003614074987848936</v>
       </c>
       <c r="M4" t="n">
-        <v>2.595708890515847</v>
+        <v>2.601780385459949</v>
       </c>
       <c r="N4" t="n">
-        <v>10.84180149044539</v>
+        <v>10.88369519509779</v>
       </c>
       <c r="O4" t="n">
-        <v>3.292689097143153</v>
+        <v>3.299044588225171</v>
       </c>
       <c r="P4" t="n">
-        <v>378.0381050824317</v>
+        <v>378.0071195568917</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20857,28 +20909,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05239128823209022</v>
+        <v>0.05486627888645867</v>
       </c>
       <c r="J5" t="n">
+        <v>382</v>
+      </c>
+      <c r="K5" t="n">
         <v>381</v>
       </c>
-      <c r="K5" t="n">
-        <v>380</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01076345014849411</v>
+        <v>0.01181734549108981</v>
       </c>
       <c r="M5" t="n">
-        <v>2.882299833807132</v>
+        <v>2.884791587398417</v>
       </c>
       <c r="N5" t="n">
-        <v>13.76731815087232</v>
+        <v>13.78576093309088</v>
       </c>
       <c r="O5" t="n">
-        <v>3.710433687707182</v>
+        <v>3.71291811559195</v>
       </c>
       <c r="P5" t="n">
-        <v>375.869526537722</v>
+        <v>375.8422346284718</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20935,28 +20987,28 @@
         <v>0.1058</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0762095656763679</v>
+        <v>0.07851720543538546</v>
       </c>
       <c r="J6" t="n">
+        <v>382</v>
+      </c>
+      <c r="K6" t="n">
         <v>381</v>
       </c>
-      <c r="K6" t="n">
-        <v>380</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03379468394020169</v>
+        <v>0.03582871582223157</v>
       </c>
       <c r="M6" t="n">
-        <v>2.372132375511057</v>
+        <v>2.375338820919829</v>
       </c>
       <c r="N6" t="n">
-        <v>9.061968544410366</v>
+        <v>9.085630149214742</v>
       </c>
       <c r="O6" t="n">
-        <v>3.010310373434999</v>
+        <v>3.014237905211654</v>
       </c>
       <c r="P6" t="n">
-        <v>371.9098229646591</v>
+        <v>371.8843764463969</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21013,28 +21065,28 @@
         <v>0.0876</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1311781178458767</v>
+        <v>0.1332166579354701</v>
       </c>
       <c r="J7" t="n">
+        <v>382</v>
+      </c>
+      <c r="K7" t="n">
         <v>381</v>
       </c>
-      <c r="K7" t="n">
-        <v>380</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0535317713576603</v>
+        <v>0.05531924560182988</v>
       </c>
       <c r="M7" t="n">
-        <v>3.172982561514329</v>
+        <v>3.170657642957271</v>
       </c>
       <c r="N7" t="n">
-        <v>16.60350433856361</v>
+        <v>16.59695141934914</v>
       </c>
       <c r="O7" t="n">
-        <v>4.074739787834753</v>
+        <v>4.073935617968101</v>
       </c>
       <c r="P7" t="n">
-        <v>365.4336336577831</v>
+        <v>365.4111545219408</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21091,28 +21143,28 @@
         <v>0.0589</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1100214551392457</v>
+        <v>-0.1069493566442263</v>
       </c>
       <c r="J8" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K8" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0265863071129826</v>
+        <v>0.02522307828953529</v>
       </c>
       <c r="M8" t="n">
-        <v>3.867599851373734</v>
+        <v>3.873396478683448</v>
       </c>
       <c r="N8" t="n">
-        <v>24.41485357312586</v>
+        <v>24.43621678374871</v>
       </c>
       <c r="O8" t="n">
-        <v>4.941138894336595</v>
+        <v>4.94330019154701</v>
       </c>
       <c r="P8" t="n">
-        <v>368.9931808172197</v>
+        <v>368.9595173805242</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21169,28 +21221,28 @@
         <v>0.0837</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05165946841105869</v>
+        <v>-0.05174760973147081</v>
       </c>
       <c r="J9" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K9" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009437773948648309</v>
+        <v>0.009527042549893894</v>
       </c>
       <c r="M9" t="n">
-        <v>2.800900929842944</v>
+        <v>2.793934534892992</v>
       </c>
       <c r="N9" t="n">
-        <v>15.43021502707849</v>
+        <v>15.38989199091701</v>
       </c>
       <c r="O9" t="n">
-        <v>3.928131238525323</v>
+        <v>3.922995283060764</v>
       </c>
       <c r="P9" t="n">
-        <v>369.0550133788049</v>
+        <v>369.0559792136455</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21247,28 +21299,28 @@
         <v>0.076</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05128984797499192</v>
+        <v>-0.05104977490867015</v>
       </c>
       <c r="J10" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K10" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006568267464985622</v>
+        <v>0.006546718627490677</v>
       </c>
       <c r="M10" t="n">
-        <v>3.57124309065383</v>
+        <v>3.563302188898098</v>
       </c>
       <c r="N10" t="n">
-        <v>21.91845526878436</v>
+        <v>21.86159788328406</v>
       </c>
       <c r="O10" t="n">
-        <v>4.68171499226345</v>
+        <v>4.675638767407515</v>
       </c>
       <c r="P10" t="n">
-        <v>366.69253636935</v>
+        <v>366.6899056970315</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21325,28 +21377,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1268502000155281</v>
+        <v>-0.1247005941562013</v>
       </c>
       <c r="J11" t="n">
+        <v>382</v>
+      </c>
+      <c r="K11" t="n">
         <v>381</v>
       </c>
-      <c r="K11" t="n">
-        <v>380</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.05614087690000591</v>
+        <v>0.05452853904197197</v>
       </c>
       <c r="M11" t="n">
-        <v>3.149574126357967</v>
+        <v>3.151416022909789</v>
       </c>
       <c r="N11" t="n">
-        <v>14.76361945921236</v>
+        <v>14.76604009801363</v>
       </c>
       <c r="O11" t="n">
-        <v>3.842345567386198</v>
+        <v>3.84266054941282</v>
       </c>
       <c r="P11" t="n">
-        <v>381.1235176097347</v>
+        <v>381.0998137432443</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21384,7 +21436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L382"/>
+  <dimension ref="A1:L383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45043,6 +45095,68 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-36.72664199927132,175.7020938938004</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-36.726626950937955,175.7029953056363</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-36.72654936773893,175.70388636932637</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-36.72647973782203,175.70477505510556</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-36.72641680334422,175.7056680709661</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>-36.72637001864655,175.7065659444468</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>-36.726266643472826,175.7074517720548</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>-36.72617361874001,175.70834094828183</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>-36.726029930471654,175.70922257239445</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>-36.72578231596753,175.71008243386683</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
